--- a/rosters/2026-07.xlsx
+++ b/rosters/2026-07.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -186,9 +186,6 @@
   </si>
   <si>
     <t>Priya, Rubesh,Shiyam</t>
-  </si>
-  <si>
-    <t>Valai, Amrdeshwara, Bala</t>
   </si>
   <si>
     <t>Valai, Amirdeshwara,Bala</t>
@@ -1171,7 +1168,7 @@
         <v>53</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>30</v>
@@ -1189,7 +1186,7 @@
         <v>51</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>30</v>
